--- a/recipes.xlsx
+++ b/recipes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pj\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1FB22AF-8E60-468B-B61F-448F5FEF719D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D567AB4E-0E46-46C6-8CD8-8F0932451831}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20520" yWindow="-120" windowWidth="20640" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -99,7 +99,7 @@
     <t>III</t>
   </si>
   <si>
-    <t>test1</t>
+    <t>images/test1</t>
   </si>
 </sst>
 </file>
